--- a/backend/data/financials_by_company/1059.HK.xlsx
+++ b/backend/data/financials_by_company/1059.HK.xlsx
@@ -642,538 +642,538 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-2157540</v>
+        <v>4528.147947</v>
       </c>
       <c r="C2" t="n">
-        <v>0.165</v>
+        <v>0.226407</v>
       </c>
       <c r="D2" t="n">
-        <v>30537000</v>
+        <v>18588000</v>
       </c>
       <c r="E2" t="n">
-        <v>-13076000</v>
+        <v>20000</v>
       </c>
       <c r="F2" t="n">
-        <v>-13076000</v>
+        <v>20000</v>
       </c>
       <c r="G2" t="n">
-        <v>5724000</v>
+        <v>5689000</v>
       </c>
       <c r="H2" t="n">
-        <v>13144000</v>
+        <v>10149000</v>
       </c>
       <c r="I2" t="n">
-        <v>58766000</v>
+        <v>55793000</v>
       </c>
       <c r="J2" t="n">
-        <v>17461000</v>
+        <v>18608000</v>
       </c>
       <c r="K2" t="n">
-        <v>4317000</v>
+        <v>8459000</v>
       </c>
       <c r="L2" t="n">
-        <v>2862000</v>
+        <v>-294000</v>
       </c>
       <c r="M2" t="n">
-        <v>505000</v>
+        <v>1105000</v>
       </c>
       <c r="N2" t="n">
-        <v>3367000</v>
+        <v>811000</v>
       </c>
       <c r="O2" t="n">
-        <v>16642460</v>
+        <v>5673528.147947</v>
       </c>
       <c r="P2" t="n">
-        <v>5724000</v>
+        <v>5689000</v>
       </c>
       <c r="Q2" t="n">
-        <v>140646000</v>
+        <v>133295000</v>
       </c>
       <c r="R2" t="n">
-        <v>262434000</v>
+        <v>217039000</v>
       </c>
       <c r="S2" t="n">
-        <v>262434000</v>
+        <v>217039000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0218</v>
+        <v>0.0262</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0218</v>
+        <v>0.0262</v>
       </c>
       <c r="V2" t="n">
-        <v>5724000</v>
+        <v>5689000</v>
       </c>
       <c r="W2" t="n">
-        <v>5724000</v>
+        <v>5689000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>5724000</v>
+        <v>5689000</v>
       </c>
       <c r="Z2" t="n">
-        <v>5724000</v>
+        <v>5689000</v>
       </c>
       <c r="AA2" t="n">
-        <v>5724000</v>
+        <v>5689000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1912000</v>
+        <v>1665000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3812000</v>
+        <v>7354000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2827000</v>
+        <v>3113000</v>
       </c>
       <c r="AE2" t="n">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-21000</v>
+        <v>-20000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2862000</v>
+        <v>-294000</v>
       </c>
       <c r="AH2" t="n">
-        <v>505000</v>
+        <v>1105000</v>
       </c>
       <c r="AI2" t="n">
-        <v>3367000</v>
+        <v>811000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11633000</v>
+        <v>5774000</v>
       </c>
       <c r="AK2" t="n">
-        <v>81880000</v>
+        <v>77502000</v>
       </c>
       <c r="AL2" t="n">
-        <v>81880000</v>
+        <v>77502000</v>
       </c>
       <c r="AM2" t="n">
-        <v>27463000</v>
+        <v>25685000</v>
       </c>
       <c r="AN2" t="n">
-        <v>54417000</v>
+        <v>51817000</v>
       </c>
       <c r="AO2" t="n">
-        <v>93513000</v>
+        <v>83276000</v>
       </c>
       <c r="AP2" t="n">
-        <v>58766000</v>
+        <v>55793000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>152279000</v>
+        <v>139069000</v>
       </c>
       <c r="AR2" t="n">
-        <v>152279000</v>
+        <v>139069000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>1334355</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.09167</v>
       </c>
       <c r="D3" t="n">
-        <v>14263000</v>
+        <v>16676000</v>
       </c>
       <c r="E3" t="n">
-        <v>8087000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8087000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9694000</v>
+        <v>4558000</v>
       </c>
       <c r="H3" t="n">
-        <v>11414000</v>
+        <v>11029000</v>
       </c>
       <c r="I3" t="n">
-        <v>54438000</v>
+        <v>54696000</v>
       </c>
       <c r="J3" t="n">
-        <v>22350000</v>
+        <v>16676000</v>
       </c>
       <c r="K3" t="n">
-        <v>10936000</v>
+        <v>5647000</v>
       </c>
       <c r="L3" t="n">
-        <v>-76000</v>
+        <v>502000</v>
       </c>
       <c r="M3" t="n">
-        <v>1290000</v>
+        <v>629000</v>
       </c>
       <c r="N3" t="n">
-        <v>1214000</v>
+        <v>1131000</v>
       </c>
       <c r="O3" t="n">
-        <v>2941355</v>
+        <v>4558000</v>
       </c>
       <c r="P3" t="n">
-        <v>9694000</v>
+        <v>4558000</v>
       </c>
       <c r="Q3" t="n">
-        <v>129439000</v>
+        <v>125093000</v>
       </c>
       <c r="R3" t="n">
-        <v>260443000</v>
+        <v>221438000</v>
       </c>
       <c r="S3" t="n">
-        <v>260443000</v>
+        <v>221438000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0372</v>
+        <v>0.0206</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0372</v>
+        <v>0.0206</v>
       </c>
       <c r="V3" t="n">
-        <v>9694000</v>
+        <v>4558000</v>
       </c>
       <c r="W3" t="n">
-        <v>9694000</v>
+        <v>4558000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9694000</v>
+        <v>4558000</v>
       </c>
       <c r="Z3" t="n">
-        <v>9694000</v>
+        <v>4558000</v>
       </c>
       <c r="AA3" t="n">
-        <v>9694000</v>
+        <v>4558000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-48000</v>
+        <v>460000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9646000</v>
+        <v>5018000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3654000</v>
+        <v>3829000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3676000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>3676000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-76000</v>
+        <v>502000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1290000</v>
+        <v>629000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1214000</v>
+        <v>1131000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-702000</v>
+        <v>2662000</v>
       </c>
       <c r="AK3" t="n">
-        <v>75001000</v>
+        <v>70397000</v>
       </c>
       <c r="AL3" t="n">
-        <v>75001000</v>
+        <v>70397000</v>
       </c>
       <c r="AM3" t="n">
-        <v>26696000</v>
+        <v>24357000</v>
       </c>
       <c r="AN3" t="n">
-        <v>48305000</v>
+        <v>46040000</v>
       </c>
       <c r="AO3" t="n">
-        <v>74299000</v>
+        <v>73059000</v>
       </c>
       <c r="AP3" t="n">
-        <v>54438000</v>
+        <v>54696000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>128737000</v>
+        <v>127755000</v>
       </c>
       <c r="AR3" t="n">
-        <v>128737000</v>
+        <v>127755000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1334355</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09167</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>16676000</v>
+        <v>14263000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>8087000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8087000</v>
       </c>
       <c r="G4" t="n">
-        <v>4558000</v>
+        <v>9694000</v>
       </c>
       <c r="H4" t="n">
-        <v>11029000</v>
+        <v>11414000</v>
       </c>
       <c r="I4" t="n">
-        <v>54696000</v>
+        <v>54438000</v>
       </c>
       <c r="J4" t="n">
-        <v>16676000</v>
+        <v>22350000</v>
       </c>
       <c r="K4" t="n">
-        <v>5647000</v>
+        <v>10936000</v>
       </c>
       <c r="L4" t="n">
-        <v>502000</v>
+        <v>-76000</v>
       </c>
       <c r="M4" t="n">
-        <v>629000</v>
+        <v>1290000</v>
       </c>
       <c r="N4" t="n">
-        <v>1131000</v>
+        <v>1214000</v>
       </c>
       <c r="O4" t="n">
-        <v>4558000</v>
+        <v>2941355</v>
       </c>
       <c r="P4" t="n">
-        <v>4558000</v>
+        <v>9694000</v>
       </c>
       <c r="Q4" t="n">
-        <v>125093000</v>
+        <v>129439000</v>
       </c>
       <c r="R4" t="n">
-        <v>221438000</v>
+        <v>260443000</v>
       </c>
       <c r="S4" t="n">
-        <v>221438000</v>
+        <v>260443000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0206</v>
+        <v>0.0372</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0206</v>
+        <v>0.0372</v>
       </c>
       <c r="V4" t="n">
-        <v>4558000</v>
+        <v>9694000</v>
       </c>
       <c r="W4" t="n">
-        <v>4558000</v>
+        <v>9694000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>4558000</v>
+        <v>9694000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4558000</v>
+        <v>9694000</v>
       </c>
       <c r="AA4" t="n">
-        <v>4558000</v>
+        <v>9694000</v>
       </c>
       <c r="AB4" t="n">
-        <v>460000</v>
+        <v>-48000</v>
       </c>
       <c r="AC4" t="n">
-        <v>5018000</v>
+        <v>9646000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3829000</v>
+        <v>3654000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-3676000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>3676000</v>
       </c>
       <c r="AG4" t="n">
-        <v>502000</v>
+        <v>-76000</v>
       </c>
       <c r="AH4" t="n">
-        <v>629000</v>
+        <v>1290000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1131000</v>
+        <v>1214000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2662000</v>
+        <v>-702000</v>
       </c>
       <c r="AK4" t="n">
-        <v>70397000</v>
+        <v>75001000</v>
       </c>
       <c r="AL4" t="n">
-        <v>70397000</v>
+        <v>75001000</v>
       </c>
       <c r="AM4" t="n">
-        <v>24357000</v>
+        <v>26696000</v>
       </c>
       <c r="AN4" t="n">
-        <v>46040000</v>
+        <v>48305000</v>
       </c>
       <c r="AO4" t="n">
-        <v>73059000</v>
+        <v>74299000</v>
       </c>
       <c r="AP4" t="n">
-        <v>54696000</v>
+        <v>54438000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>127755000</v>
+        <v>128737000</v>
       </c>
       <c r="AR4" t="n">
-        <v>127755000</v>
+        <v>128737000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>4528.147947</v>
+        <v>-2157540</v>
       </c>
       <c r="C5" t="n">
-        <v>0.226407</v>
+        <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>18588000</v>
+        <v>30537000</v>
       </c>
       <c r="E5" t="n">
-        <v>20000</v>
+        <v>-13076000</v>
       </c>
       <c r="F5" t="n">
-        <v>20000</v>
+        <v>-13076000</v>
       </c>
       <c r="G5" t="n">
-        <v>5689000</v>
+        <v>5724000</v>
       </c>
       <c r="H5" t="n">
-        <v>10149000</v>
+        <v>13144000</v>
       </c>
       <c r="I5" t="n">
-        <v>55793000</v>
+        <v>58766000</v>
       </c>
       <c r="J5" t="n">
-        <v>18608000</v>
+        <v>17461000</v>
       </c>
       <c r="K5" t="n">
-        <v>8459000</v>
+        <v>4317000</v>
       </c>
       <c r="L5" t="n">
-        <v>-294000</v>
+        <v>2862000</v>
       </c>
       <c r="M5" t="n">
-        <v>1105000</v>
+        <v>505000</v>
       </c>
       <c r="N5" t="n">
-        <v>811000</v>
+        <v>3367000</v>
       </c>
       <c r="O5" t="n">
-        <v>5673528.147947</v>
+        <v>16642460</v>
       </c>
       <c r="P5" t="n">
-        <v>5689000</v>
+        <v>5724000</v>
       </c>
       <c r="Q5" t="n">
-        <v>133295000</v>
+        <v>140646000</v>
       </c>
       <c r="R5" t="n">
-        <v>217039000</v>
+        <v>262434000</v>
       </c>
       <c r="S5" t="n">
-        <v>217039000</v>
+        <v>262434000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0262</v>
+        <v>0.0218</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0262</v>
+        <v>0.0218</v>
       </c>
       <c r="V5" t="n">
-        <v>5689000</v>
+        <v>5724000</v>
       </c>
       <c r="W5" t="n">
-        <v>5689000</v>
+        <v>5724000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>5689000</v>
+        <v>5724000</v>
       </c>
       <c r="Z5" t="n">
-        <v>5689000</v>
+        <v>5724000</v>
       </c>
       <c r="AA5" t="n">
-        <v>5689000</v>
+        <v>5724000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1665000</v>
+        <v>-1912000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7354000</v>
+        <v>3812000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3113000</v>
+        <v>2827000</v>
       </c>
       <c r="AE5" t="n">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-20000</v>
+        <v>-21000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-294000</v>
+        <v>2862000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1105000</v>
+        <v>505000</v>
       </c>
       <c r="AI5" t="n">
-        <v>811000</v>
+        <v>3367000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5774000</v>
+        <v>11633000</v>
       </c>
       <c r="AK5" t="n">
-        <v>77502000</v>
+        <v>81880000</v>
       </c>
       <c r="AL5" t="n">
-        <v>77502000</v>
+        <v>81880000</v>
       </c>
       <c r="AM5" t="n">
-        <v>25685000</v>
+        <v>27463000</v>
       </c>
       <c r="AN5" t="n">
-        <v>51817000</v>
+        <v>54417000</v>
       </c>
       <c r="AO5" t="n">
-        <v>83276000</v>
+        <v>93513000</v>
       </c>
       <c r="AP5" t="n">
-        <v>55793000</v>
+        <v>58766000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>139069000</v>
+        <v>152279000</v>
       </c>
       <c r="AR5" t="n">
-        <v>139069000</v>
+        <v>152279000</v>
       </c>
     </row>
   </sheetData>
@@ -1464,168 +1464,162 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>312528506</v>
+        <v>217039000</v>
       </c>
       <c r="C2" t="n">
-        <v>312528506</v>
+        <v>217039000</v>
       </c>
       <c r="D2" t="n">
-        <v>6271000</v>
+        <v>4427000</v>
       </c>
       <c r="E2" t="n">
-        <v>165412000</v>
+        <v>107663000</v>
       </c>
       <c r="F2" t="n">
-        <v>165412000</v>
+        <v>107663000</v>
       </c>
       <c r="G2" t="n">
-        <v>97644000</v>
+        <v>86549000</v>
       </c>
       <c r="H2" t="n">
-        <v>165412000</v>
+        <v>107663000</v>
       </c>
       <c r="I2" t="n">
-        <v>6271000</v>
+        <v>4427000</v>
       </c>
       <c r="J2" t="n">
-        <v>165412000</v>
+        <v>107663000</v>
       </c>
       <c r="K2" t="n">
-        <v>165412000</v>
+        <v>107663000</v>
       </c>
       <c r="L2" t="n">
-        <v>165412000</v>
+        <v>107663000</v>
       </c>
       <c r="M2" t="n">
-        <v>165412000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1651216000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>816413000</v>
-      </c>
+        <v>107663000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>31253000</v>
+        <v>21704000</v>
       </c>
       <c r="Q2" t="n">
-        <v>31253000</v>
+        <v>21704000</v>
       </c>
       <c r="R2" t="n">
-        <v>77004000</v>
+        <v>109017000</v>
       </c>
       <c r="S2" t="n">
-        <v>3072000</v>
+        <v>17771000</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>16018000</v>
       </c>
       <c r="U2" t="n">
-        <v>3072000</v>
+        <v>1753000</v>
       </c>
       <c r="V2" t="n">
-        <v>3072000</v>
+        <v>1753000</v>
       </c>
       <c r="W2" t="n">
-        <v>73932000</v>
+        <v>91246000</v>
       </c>
       <c r="X2" t="n">
-        <v>3199000</v>
+        <v>2674000</v>
       </c>
       <c r="Y2" t="n">
-        <v>3199000</v>
+        <v>2674000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1259000</v>
+        <v>1062000</v>
       </c>
       <c r="AA2" t="n">
-        <v>43557000</v>
+        <v>62540000</v>
       </c>
       <c r="AB2" t="n">
-        <v>40213000</v>
+        <v>58325000</v>
       </c>
       <c r="AC2" t="n">
-        <v>36000</v>
+        <v>26000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3308000</v>
+        <v>4189000</v>
       </c>
       <c r="AE2" t="n">
-        <v>242416000</v>
+        <v>216680000</v>
       </c>
       <c r="AF2" t="n">
-        <v>70840000</v>
+        <v>38885000</v>
       </c>
       <c r="AG2" t="n">
-        <v>17665000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5530000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>43893000</v>
+        <v>38885000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-146049000</v>
+        <v>-297386000</v>
       </c>
       <c r="AM2" t="n">
-        <v>189942000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>336271000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38885000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>174360000</v>
+        <v>320268000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1213000</v>
+        <v>400000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14369000</v>
+        <v>15603000</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>171576000</v>
+        <v>177795000</v>
       </c>
       <c r="AT2" t="n">
-        <v>20255000</v>
+        <v>23105000</v>
       </c>
       <c r="AU2" t="n">
-        <v>9073000</v>
+        <v>10013000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3657000</v>
+        <v>5807000</v>
       </c>
       <c r="AW2" t="n">
-        <v>7525000</v>
+        <v>7285000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2628000</v>
+        <v>20735000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2705000</v>
+        <v>285000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>36263000</v>
+        <v>14822000</v>
       </c>
       <c r="BA2" t="n">
-        <v>109725000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>417000</v>
-      </c>
+        <v>118848000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>109308000</v>
+        <v>118848000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>260443000</v>
@@ -1634,37 +1628,37 @@
         <v>260443000</v>
       </c>
       <c r="D3" t="n">
-        <v>5011000</v>
+        <v>5121000</v>
       </c>
       <c r="E3" t="n">
-        <v>134593000</v>
+        <v>133279000</v>
       </c>
       <c r="F3" t="n">
-        <v>134593000</v>
+        <v>133279000</v>
       </c>
       <c r="G3" t="n">
-        <v>88149000</v>
+        <v>84482000</v>
       </c>
       <c r="H3" t="n">
-        <v>134593000</v>
+        <v>133279000</v>
       </c>
       <c r="I3" t="n">
-        <v>5011000</v>
+        <v>5121000</v>
       </c>
       <c r="J3" t="n">
-        <v>134593000</v>
+        <v>133279000</v>
       </c>
       <c r="K3" t="n">
-        <v>134593000</v>
+        <v>133279000</v>
       </c>
       <c r="L3" t="n">
-        <v>134593000</v>
+        <v>133279000</v>
       </c>
       <c r="M3" t="n">
-        <v>134593000</v>
+        <v>133279000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1668781000</v>
+        <v>-1668696000</v>
       </c>
       <c r="O3" t="n">
         <v>806741000</v>
@@ -1676,119 +1670,121 @@
         <v>26044000</v>
       </c>
       <c r="R3" t="n">
-        <v>89358000</v>
+        <v>76908000</v>
       </c>
       <c r="S3" t="n">
-        <v>1944000</v>
+        <v>2393000</v>
       </c>
       <c r="T3" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1924000</v>
+        <v>2393000</v>
       </c>
       <c r="V3" t="n">
-        <v>1924000</v>
+        <v>2393000</v>
       </c>
       <c r="W3" t="n">
-        <v>87414000</v>
+        <v>74515000</v>
       </c>
       <c r="X3" t="n">
-        <v>3087000</v>
+        <v>2728000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3087000</v>
+        <v>2728000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1123000</v>
+        <v>1053000</v>
       </c>
       <c r="AA3" t="n">
-        <v>51802000</v>
+        <v>46638000</v>
       </c>
       <c r="AB3" t="n">
-        <v>43873000</v>
+        <v>43392000</v>
       </c>
       <c r="AC3" t="n">
-        <v>59000</v>
+        <v>26000</v>
       </c>
       <c r="AD3" t="n">
-        <v>7870000</v>
+        <v>3220000</v>
       </c>
       <c r="AE3" t="n">
-        <v>223951000</v>
+        <v>210187000</v>
       </c>
       <c r="AF3" t="n">
-        <v>48388000</v>
+        <v>51190000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>7165000</v>
       </c>
       <c r="AH3" t="n">
-        <v>6013000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7165000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>7165000</v>
+      </c>
       <c r="AK3" t="n">
-        <v>40080000</v>
+        <v>44025000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-291712000</v>
+        <v>-271931000</v>
       </c>
       <c r="AM3" t="n">
-        <v>331792000</v>
+        <v>315956000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40080000</v>
+        <v>44025000</v>
       </c>
       <c r="AO3" t="n">
-        <v>315586000</v>
+        <v>294180000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1714000</v>
+        <v>2133000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14492000</v>
+        <v>19643000</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>175563000</v>
+        <v>158997000</v>
       </c>
       <c r="AT3" t="n">
-        <v>23150000</v>
+        <v>20934000</v>
       </c>
       <c r="AU3" t="n">
-        <v>9079000</v>
+        <v>10463000</v>
       </c>
       <c r="AV3" t="n">
-        <v>4594000</v>
+        <v>1760000</v>
       </c>
       <c r="AW3" t="n">
-        <v>9477000</v>
+        <v>8711000</v>
       </c>
       <c r="AX3" t="n">
-        <v>2787000</v>
+        <v>5854000</v>
       </c>
       <c r="AY3" t="n">
-        <v>747000</v>
+        <v>112000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>34092000</v>
+        <v>23837000</v>
       </c>
       <c r="BA3" t="n">
-        <v>114787000</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>14027000</v>
-      </c>
+        <v>108260000</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>100760000</v>
+        <v>108260000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>260443000</v>
@@ -1797,37 +1793,37 @@
         <v>260443000</v>
       </c>
       <c r="D4" t="n">
-        <v>5121000</v>
+        <v>5011000</v>
       </c>
       <c r="E4" t="n">
-        <v>133279000</v>
+        <v>134593000</v>
       </c>
       <c r="F4" t="n">
-        <v>133279000</v>
+        <v>134593000</v>
       </c>
       <c r="G4" t="n">
-        <v>84482000</v>
+        <v>88149000</v>
       </c>
       <c r="H4" t="n">
-        <v>133279000</v>
+        <v>134593000</v>
       </c>
       <c r="I4" t="n">
-        <v>5121000</v>
+        <v>5011000</v>
       </c>
       <c r="J4" t="n">
-        <v>133279000</v>
+        <v>134593000</v>
       </c>
       <c r="K4" t="n">
-        <v>133279000</v>
+        <v>134593000</v>
       </c>
       <c r="L4" t="n">
-        <v>133279000</v>
+        <v>134593000</v>
       </c>
       <c r="M4" t="n">
-        <v>133279000</v>
+        <v>134593000</v>
       </c>
       <c r="N4" t="n">
-        <v>-1668696000</v>
+        <v>-1668781000</v>
       </c>
       <c r="O4" t="n">
         <v>806741000</v>
@@ -1839,271 +1835,275 @@
         <v>26044000</v>
       </c>
       <c r="R4" t="n">
-        <v>76908000</v>
+        <v>89358000</v>
       </c>
       <c r="S4" t="n">
-        <v>2393000</v>
+        <v>1944000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="U4" t="n">
-        <v>2393000</v>
+        <v>1924000</v>
       </c>
       <c r="V4" t="n">
-        <v>2393000</v>
+        <v>1924000</v>
       </c>
       <c r="W4" t="n">
-        <v>74515000</v>
+        <v>87414000</v>
       </c>
       <c r="X4" t="n">
-        <v>2728000</v>
+        <v>3087000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2728000</v>
+        <v>3087000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1053000</v>
+        <v>1123000</v>
       </c>
       <c r="AA4" t="n">
-        <v>46638000</v>
+        <v>51802000</v>
       </c>
       <c r="AB4" t="n">
-        <v>43392000</v>
+        <v>43873000</v>
       </c>
       <c r="AC4" t="n">
-        <v>26000</v>
+        <v>59000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3220000</v>
+        <v>7870000</v>
       </c>
       <c r="AE4" t="n">
-        <v>210187000</v>
+        <v>223951000</v>
       </c>
       <c r="AF4" t="n">
-        <v>51190000</v>
+        <v>48388000</v>
       </c>
       <c r="AG4" t="n">
-        <v>7165000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7165000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>7165000</v>
-      </c>
+        <v>6013000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>44025000</v>
+        <v>40080000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-271931000</v>
+        <v>-291712000</v>
       </c>
       <c r="AM4" t="n">
-        <v>315956000</v>
+        <v>331792000</v>
       </c>
       <c r="AN4" t="n">
-        <v>44025000</v>
+        <v>40080000</v>
       </c>
       <c r="AO4" t="n">
-        <v>294180000</v>
+        <v>315586000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2133000</v>
+        <v>1714000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19643000</v>
+        <v>14492000</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>158997000</v>
+        <v>175563000</v>
       </c>
       <c r="AT4" t="n">
-        <v>20934000</v>
+        <v>23150000</v>
       </c>
       <c r="AU4" t="n">
-        <v>10463000</v>
+        <v>9079000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1760000</v>
+        <v>4594000</v>
       </c>
       <c r="AW4" t="n">
-        <v>8711000</v>
+        <v>9477000</v>
       </c>
       <c r="AX4" t="n">
-        <v>5854000</v>
+        <v>2787000</v>
       </c>
       <c r="AY4" t="n">
-        <v>112000</v>
+        <v>747000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23837000</v>
+        <v>34092000</v>
       </c>
       <c r="BA4" t="n">
-        <v>108260000</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+        <v>114787000</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>14027000</v>
+      </c>
       <c r="BC4" t="n">
-        <v>108260000</v>
+        <v>100760000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>217039000</v>
+        <v>312528506</v>
       </c>
       <c r="C5" t="n">
-        <v>217039000</v>
+        <v>312528506</v>
       </c>
       <c r="D5" t="n">
-        <v>4427000</v>
+        <v>6271000</v>
       </c>
       <c r="E5" t="n">
-        <v>107663000</v>
+        <v>165412000</v>
       </c>
       <c r="F5" t="n">
-        <v>107663000</v>
+        <v>165412000</v>
       </c>
       <c r="G5" t="n">
-        <v>86549000</v>
+        <v>97644000</v>
       </c>
       <c r="H5" t="n">
-        <v>107663000</v>
+        <v>165412000</v>
       </c>
       <c r="I5" t="n">
-        <v>4427000</v>
+        <v>6271000</v>
       </c>
       <c r="J5" t="n">
-        <v>107663000</v>
+        <v>165412000</v>
       </c>
       <c r="K5" t="n">
-        <v>107663000</v>
+        <v>165412000</v>
       </c>
       <c r="L5" t="n">
-        <v>107663000</v>
+        <v>165412000</v>
       </c>
       <c r="M5" t="n">
-        <v>107663000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>165412000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1651216000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>816413000</v>
+      </c>
       <c r="P5" t="n">
-        <v>21704000</v>
+        <v>31253000</v>
       </c>
       <c r="Q5" t="n">
-        <v>21704000</v>
+        <v>31253000</v>
       </c>
       <c r="R5" t="n">
-        <v>109017000</v>
+        <v>77004000</v>
       </c>
       <c r="S5" t="n">
-        <v>17771000</v>
+        <v>3072000</v>
       </c>
       <c r="T5" t="n">
-        <v>16018000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1753000</v>
+        <v>3072000</v>
       </c>
       <c r="V5" t="n">
-        <v>1753000</v>
+        <v>3072000</v>
       </c>
       <c r="W5" t="n">
-        <v>91246000</v>
+        <v>73932000</v>
       </c>
       <c r="X5" t="n">
-        <v>2674000</v>
+        <v>3199000</v>
       </c>
       <c r="Y5" t="n">
-        <v>2674000</v>
+        <v>3199000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1062000</v>
+        <v>1259000</v>
       </c>
       <c r="AA5" t="n">
-        <v>62540000</v>
+        <v>43557000</v>
       </c>
       <c r="AB5" t="n">
-        <v>58325000</v>
+        <v>40213000</v>
       </c>
       <c r="AC5" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="AD5" t="n">
-        <v>4189000</v>
+        <v>3308000</v>
       </c>
       <c r="AE5" t="n">
-        <v>216680000</v>
+        <v>242416000</v>
       </c>
       <c r="AF5" t="n">
-        <v>38885000</v>
+        <v>70840000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>17665000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>5530000</v>
+      </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>38885000</v>
+        <v>43893000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-297386000</v>
+        <v>-146049000</v>
       </c>
       <c r="AM5" t="n">
-        <v>336271000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>38885000</v>
-      </c>
+        <v>189942000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>320268000</v>
+        <v>174360000</v>
       </c>
       <c r="AP5" t="n">
-        <v>400000</v>
+        <v>1213000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15603000</v>
+        <v>14369000</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>177795000</v>
+        <v>171576000</v>
       </c>
       <c r="AT5" t="n">
-        <v>23105000</v>
+        <v>20255000</v>
       </c>
       <c r="AU5" t="n">
-        <v>10013000</v>
+        <v>9073000</v>
       </c>
       <c r="AV5" t="n">
-        <v>5807000</v>
+        <v>3657000</v>
       </c>
       <c r="AW5" t="n">
-        <v>7285000</v>
+        <v>7525000</v>
       </c>
       <c r="AX5" t="n">
-        <v>20735000</v>
+        <v>2628000</v>
       </c>
       <c r="AY5" t="n">
-        <v>285000</v>
+        <v>2705000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14822000</v>
+        <v>36263000</v>
       </c>
       <c r="BA5" t="n">
-        <v>118848000</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>109725000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>417000</v>
+      </c>
       <c r="BC5" t="n">
-        <v>118848000</v>
+        <v>109308000</v>
       </c>
     </row>
   </sheetData>
@@ -2329,458 +2329,458 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-5237000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>3171000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2315000</v>
+      </c>
       <c r="E2" t="n">
-        <v>14881000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-12496000</v>
+        <v>-10490000</v>
       </c>
       <c r="G2" t="n">
-        <v>109308000</v>
+        <v>118848000</v>
       </c>
       <c r="H2" t="n">
-        <v>100760000</v>
+        <v>95472000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1249000</v>
+        <v>13835000</v>
       </c>
       <c r="J2" t="n">
-        <v>9797000</v>
+        <v>9541000</v>
       </c>
       <c r="K2" t="n">
-        <v>10964000</v>
+        <v>-818000</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-252000</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>14881000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>14881000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2315000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2315000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2315000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2315000</v>
+      </c>
       <c r="U2" t="n">
-        <v>-8426000</v>
+        <v>-3302000</v>
       </c>
       <c r="V2" t="n">
-        <v>3320000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>513000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>513000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
+        <v>635000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>-12474000</v>
+        <v>-10490000</v>
       </c>
       <c r="AA2" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-12496000</v>
+        <v>-10490000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7259000</v>
+        <v>13661000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-73000</v>
+        <v>-1300000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-19967000</v>
+        <v>-2816000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-10574000</v>
+        <v>-473000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-8203000</v>
+        <v>481000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2712000</v>
+        <v>2000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3902000</v>
+        <v>-2529000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-3454000</v>
+        <v>294000</v>
       </c>
       <c r="AK2" t="n">
-        <v>159000</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>13144000</v>
+        <v>10149000</v>
       </c>
       <c r="AM2" t="n">
-        <v>13144000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>13531000</v>
-      </c>
+        <v>10149000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>3812000</v>
+        <v>7354000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-5861000</v>
+        <v>-6612000</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>11764000</v>
       </c>
       <c r="F3" t="n">
-        <v>-9021000</v>
+        <v>-16811000</v>
       </c>
       <c r="G3" t="n">
-        <v>100760000</v>
+        <v>108260000</v>
       </c>
       <c r="H3" t="n">
-        <v>108260000</v>
+        <v>118848000</v>
       </c>
       <c r="I3" t="n">
-        <v>688000</v>
+        <v>-8435000</v>
       </c>
       <c r="J3" t="n">
-        <v>-8188000</v>
+        <v>-2153000</v>
       </c>
       <c r="K3" t="n">
-        <v>-3222000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>919000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-7369000</v>
+      </c>
       <c r="M3" t="n">
-        <v>-200000</v>
+        <v>-629000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>11764000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>11764000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-7369000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-7369000</v>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>-8126000</v>
+        <v>-13271000</v>
       </c>
       <c r="V3" t="n">
-        <v>571000</v>
+        <v>574000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2264000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5527000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-7791000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-9021000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
+        <v>-16811000</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-9021000</v>
+        <v>-16811000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3160000</v>
+        <v>10199000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-535000</v>
+        <v>-310000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-9188000</v>
+        <v>-5863000</v>
       </c>
       <c r="AF3" t="n">
-        <v>4593000</v>
+        <v>-656000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2920000</v>
+        <v>-5242000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-4918000</v>
+        <v>-5000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-11783000</v>
+        <v>49000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-216000</v>
+        <v>53000</v>
       </c>
       <c r="AK3" t="n">
-        <v>25000</v>
+        <v>142000</v>
       </c>
       <c r="AL3" t="n">
-        <v>11414000</v>
+        <v>11029000</v>
       </c>
       <c r="AM3" t="n">
-        <v>11414000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-11763000</v>
-      </c>
+        <v>11029000</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>101000</v>
+        <v>130000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9646000</v>
+        <v>5018000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-6612000</v>
+        <v>-5861000</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>11764000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-16811000</v>
+        <v>-9021000</v>
       </c>
       <c r="G4" t="n">
+        <v>100760000</v>
+      </c>
+      <c r="H4" t="n">
         <v>108260000</v>
       </c>
-      <c r="H4" t="n">
-        <v>118848000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-8435000</v>
+        <v>688000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2153000</v>
+        <v>-8188000</v>
       </c>
       <c r="K4" t="n">
-        <v>919000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-7369000</v>
-      </c>
+        <v>-3222000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-629000</v>
+        <v>-200000</v>
       </c>
       <c r="N4" t="n">
-        <v>11764000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>11764000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-7369000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-7369000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-13271000</v>
+        <v>-8126000</v>
       </c>
       <c r="V4" t="n">
-        <v>574000</v>
+        <v>571000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-2264000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5527000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-7791000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-16811000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>-9021000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
       <c r="AB4" t="n">
-        <v>-16811000</v>
+        <v>-9021000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10199000</v>
+        <v>3160000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-310000</v>
+        <v>-535000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-5863000</v>
+        <v>-9188000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-656000</v>
+        <v>4593000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5242000</v>
+        <v>2920000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5000</v>
+        <v>-4918000</v>
       </c>
       <c r="AI4" t="n">
-        <v>49000</v>
+        <v>-11783000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>53000</v>
+        <v>-216000</v>
       </c>
       <c r="AK4" t="n">
-        <v>142000</v>
+        <v>25000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11029000</v>
+        <v>11414000</v>
       </c>
       <c r="AM4" t="n">
-        <v>11029000</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>11414000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-11763000</v>
+      </c>
       <c r="AO4" t="n">
-        <v>130000</v>
+        <v>101000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5018000</v>
+        <v>9646000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>3171000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2315000</v>
-      </c>
+        <v>-5237000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>14881000</v>
       </c>
       <c r="F5" t="n">
-        <v>-10490000</v>
+        <v>-12496000</v>
       </c>
       <c r="G5" t="n">
-        <v>118848000</v>
+        <v>109308000</v>
       </c>
       <c r="H5" t="n">
-        <v>95472000</v>
+        <v>100760000</v>
       </c>
       <c r="I5" t="n">
-        <v>13835000</v>
+        <v>-1249000</v>
       </c>
       <c r="J5" t="n">
-        <v>9541000</v>
+        <v>9797000</v>
       </c>
       <c r="K5" t="n">
-        <v>-818000</v>
+        <v>10964000</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-252000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>14881000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2315000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2315000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2315000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2315000</v>
-      </c>
+        <v>14881000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-3302000</v>
+        <v>-8426000</v>
       </c>
       <c r="V5" t="n">
-        <v>635000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+        <v>3320000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>513000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>513000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" t="n">
-        <v>-10490000</v>
+        <v>-12474000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10490000</v>
+        <v>-12496000</v>
       </c>
       <c r="AC5" t="n">
-        <v>13661000</v>
+        <v>7259000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1300000</v>
+        <v>-73000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2816000</v>
+        <v>-19967000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-473000</v>
+        <v>-10574000</v>
       </c>
       <c r="AG5" t="n">
-        <v>481000</v>
+        <v>-8203000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2000</v>
+        <v>2712000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2529000</v>
+        <v>-3902000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>294000</v>
+        <v>-3454000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>159000</v>
       </c>
       <c r="AL5" t="n">
-        <v>10149000</v>
+        <v>13144000</v>
       </c>
       <c r="AM5" t="n">
-        <v>10149000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>13144000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13531000</v>
+      </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>128000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7354000</v>
+        <v>3812000</v>
       </c>
     </row>
   </sheetData>
@@ -3340,187 +3340,187 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -3618,28 +3618,28 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.445</v>
+        <v>0.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0.42</v>
+        <v>0.375</v>
       </c>
       <c r="V2" t="n">
-        <v>0.405</v>
+        <v>0.37</v>
       </c>
       <c r="W2" t="n">
-        <v>0.455</v>
+        <v>0.415</v>
       </c>
       <c r="X2" t="n">
-        <v>0.445</v>
+        <v>0.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.42</v>
+        <v>0.375</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.405</v>
+        <v>0.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.455</v>
+        <v>0.415</v>
       </c>
       <c r="AB2" t="n">
         <v>1394755200</v>
@@ -3651,31 +3651,31 @@
         <v>4.01</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.303</v>
+        <v>0.323</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>33000</v>
+        <v>60000</v>
       </c>
       <c r="AH2" t="n">
-        <v>33000</v>
+        <v>60000</v>
       </c>
       <c r="AI2" t="n">
-        <v>14188</v>
+        <v>198912</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17253</v>
+        <v>1115756</v>
       </c>
       <c r="AK2" t="n">
-        <v>17253</v>
+        <v>1115756</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.445</v>
+        <v>0.38</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3684,13 +3684,13 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>166889904</v>
+        <v>142512736</v>
       </c>
       <c r="AQ2" t="n">
-        <v>166889910</v>
+        <v>142512732</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.188</v>
+        <v>0.25</v>
       </c>
       <c r="AS2" t="n">
         <v>0.51</v>
@@ -3702,13 +3702,13 @@
         <v>0.162</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.1347111</v>
+        <v>0.9689669</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.4167</v>
+        <v>0.4097</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.4043</v>
+        <v>0.40715</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>26915684</v>
+        <v>2538540</v>
       </c>
       <c r="BD2" t="n">
         <v>0.13358</v>
@@ -3749,7 +3749,7 @@
         <v>0.591</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.75296104</v>
+        <v>0.64297795</v>
       </c>
       <c r="BL2" t="n">
         <v>1751241600</v>
@@ -3781,16 +3781,16 @@
         <v>1523318400</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.183</v>
+        <v>0.017</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.734</v>
+        <v>0.164</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.3056996</v>
+        <v>0.43396223</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.1</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.445</v>
+        <v>0.38</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -3906,140 +3906,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>1782104772</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>finmb_4483944</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>KANTONE HOLDING</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Kantone Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
         <v>946949400000</v>
       </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>1780384233</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>finmb_4483944</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Kantone Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>KANTONE HOLDING</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>0.37 - 0.415</t>
+        </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>0.405 - 0.455</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
           <t>HKSE</t>
         </is>
       </c>
+      <c r="DX2" t="n">
+        <v>198912</v>
+      </c>
       <c r="DY2" t="n">
-        <v>14188</v>
+        <v>0.13</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1.3670213</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>0.188 - 0.51</t>
-        </is>
+        <v>0.52</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>0.25 - 0.51</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.13</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0.065</v>
+        <v>-0.25490195</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0.12745097</v>
+        <v>43.39622</v>
       </c>
       <c r="EE2" t="n">
-        <v>130.56996</v>
+        <v>1740579381</v>
       </c>
       <c r="EF2" t="n">
         <v>1740579381</v>
       </c>
-      <c r="EG2" t="n">
-        <v>1740579381</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.05</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.05</v>
+        <v>-0.029700011</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.028299987</v>
+        <v>-0.07249209</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.06791454</v>
+        <v>-0.027150005</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.04069999</v>
+        <v>-0.06668305400000001</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.10066779</v>
+        <v>15</v>
       </c>
       <c r="EN2" t="n">
         <v>15</v>
       </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+      <c r="EO2" t="b">
+        <v>0</v>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
